--- a/Pasta_Biwenger_Portatil_Gris.xlsx
+++ b/Pasta_Biwenger_Portatil_Gris.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juliu\Documents\biwenger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A8BF2C-7037-4E0D-98F1-4E5E9D2AFCFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{974DAC48-D3B4-48E6-BC09-CE758F82E04E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="995" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="995" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Automate" sheetId="1" r:id="rId1"/>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="L1" s="10">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="L1" s="10">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="L1" s="6">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="L1" s="6">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="L1" s="6">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -11554,7 +11554,7 @@
       </c>
       <c r="L1" s="10">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="J1" s="6">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -12925,7 +12925,7 @@
       </c>
       <c r="L1" s="10">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -13578,7 +13578,7 @@
       </c>
       <c r="L1" s="10">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -14173,13 +14173,11 @@
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="F28"/>
       <c r="J28" s="5" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="F29"/>
       <c r="J29" t="s">
         <v>76</v>
       </c>
@@ -14307,7 +14305,7 @@
       </c>
       <c r="L1" s="10">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -14990,7 +14988,7 @@
       </c>
       <c r="L1" s="10">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -15646,7 +15644,7 @@
       </c>
       <c r="L1" s="10">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">

--- a/Pasta_Biwenger_Portatil_Gris.xlsx
+++ b/Pasta_Biwenger_Portatil_Gris.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="995" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="995" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guacamayos" sheetId="1" state="visible" r:id="rId1"/>
@@ -1750,7 +1750,7 @@
         <v/>
       </c>
       <c r="H2" s="7" t="n">
-        <v>34510000</v>
+        <v>41690000</v>
       </c>
       <c r="I2" s="7" t="n">
         <v>1130000</v>
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="K2" s="4" t="n">
-        <v>45939.4575</v>
+        <v>45940.52256944445</v>
       </c>
     </row>
     <row r="3">
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="H2" s="7" t="n">
-        <v>43850000</v>
+        <v>44650000</v>
       </c>
       <c r="I2" s="7" t="n">
         <v>930000</v>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="K2" s="4" t="n">
-        <v>45939.4575</v>
+        <v>45940.52256944445</v>
       </c>
     </row>
     <row r="3">
@@ -3580,7 +3580,7 @@
         <v/>
       </c>
       <c r="H2" s="7" t="n">
-        <v>37640000</v>
+        <v>38190000</v>
       </c>
       <c r="I2" s="7" t="n">
         <v>1110000</v>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="K2" s="4" t="n">
-        <v>45939.4575</v>
+        <v>45940.52256944445</v>
       </c>
     </row>
     <row r="3">
@@ -4573,7 +4573,7 @@
         <v/>
       </c>
       <c r="H2" s="7" t="n">
-        <v>11290000</v>
+        <v>11170000</v>
       </c>
       <c r="I2" s="7" t="n">
         <v>1310000</v>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="K2" s="4" t="n">
-        <v>45939.4575</v>
+        <v>45940.52256944445</v>
       </c>
     </row>
     <row r="3">
@@ -5127,7 +5127,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="25" t="n">
-        <v>45939.4575</v>
+        <v>45940.52256944445</v>
       </c>
     </row>
     <row r="3">
@@ -10402,7 +10402,7 @@
         </is>
       </c>
       <c r="K2" s="25" t="n">
-        <v>45939.4575</v>
+        <v>45940.52256944445</v>
       </c>
     </row>
     <row r="3" ht="13" customHeight="1" thickBot="1">
@@ -11692,7 +11692,7 @@
         <v/>
       </c>
       <c r="H2" s="7" t="n">
-        <v>40510000</v>
+        <v>40840000</v>
       </c>
       <c r="I2" s="7" t="n">
         <v>760000</v>
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="K2" s="4" t="n">
-        <v>45939.4575</v>
+        <v>45940.52256944445</v>
       </c>
     </row>
     <row r="3">
@@ -12499,9 +12499,9 @@
           <t>Total Ingresos</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Valor Inicial</t>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Valor Actual</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
@@ -12541,8 +12541,8 @@
         <f>SUM(F:F)</f>
         <v/>
       </c>
-      <c r="H2" s="6" t="n">
-        <v>21250000</v>
+      <c r="H2" s="7" t="n">
+        <v>37700000</v>
       </c>
       <c r="I2" s="7" t="n">
         <v>930000</v>
@@ -12553,7 +12553,7 @@
         </is>
       </c>
       <c r="K2" s="4" t="n">
-        <v>45939.4575</v>
+        <v>45940.52256944445</v>
       </c>
     </row>
     <row r="3">
@@ -12606,9 +12606,9 @@
           <t>Total Perdidas</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Valor Actual</t>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>Valor Inicial</t>
         </is>
       </c>
       <c r="I4" s="7" t="n">
@@ -12650,8 +12650,8 @@
         <f>SUM(D:D)</f>
         <v/>
       </c>
-      <c r="H5" s="7" t="n">
-        <v>41920000</v>
+      <c r="H5" s="6" t="n">
+        <v>21250000</v>
       </c>
       <c r="I5" s="7" t="n">
         <v>750000</v>
@@ -12853,7 +12853,7 @@
         <v/>
       </c>
       <c r="H11" s="6">
-        <f>G11-G8+H5-H2-H8</f>
+        <f>G11-G8+H2-H5-H8</f>
         <v/>
       </c>
       <c r="J11" t="inlineStr">
@@ -13022,7 +13022,7 @@
         <v>145200</v>
       </c>
       <c r="H17" s="12">
-        <f>G11+H5/4</f>
+        <f>G11+H2/4</f>
         <v/>
       </c>
       <c r="I17" s="7" t="n"/>
@@ -13567,7 +13567,7 @@
         <v/>
       </c>
       <c r="H2" s="7" t="n">
-        <v>44850000</v>
+        <v>44740000</v>
       </c>
       <c r="I2" s="7" t="n">
         <v>990000</v>
@@ -13578,7 +13578,7 @@
         </is>
       </c>
       <c r="K2" s="4" t="n">
-        <v>45939.4575</v>
+        <v>45940.52256944445</v>
       </c>
     </row>
     <row r="3">
@@ -14451,7 +14451,7 @@
         <v/>
       </c>
       <c r="H2" s="7" t="n">
-        <v>36970000</v>
+        <v>41610000</v>
       </c>
       <c r="I2" s="7" t="n">
         <v>620000</v>
@@ -14462,7 +14462,7 @@
         </is>
       </c>
       <c r="K2" s="4" t="n">
-        <v>45939.4575</v>
+        <v>45940.52256944445</v>
       </c>
     </row>
     <row r="3">
@@ -15165,6 +15165,14 @@
       </c>
     </row>
     <row r="24">
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Jonathan Viera</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="n">
+        <v>4500000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>Aarón Ochoa</t>
@@ -15440,7 +15448,7 @@
         <v/>
       </c>
       <c r="H2" s="7" t="n">
-        <v>38120000</v>
+        <v>37790000</v>
       </c>
       <c r="I2" s="7" t="n">
         <v>710000</v>
@@ -15451,7 +15459,7 @@
         </is>
       </c>
       <c r="K2" s="4" t="n">
-        <v>45939.4575</v>
+        <v>45940.52256944445</v>
       </c>
     </row>
     <row r="3">
@@ -16374,7 +16382,7 @@
         </is>
       </c>
       <c r="K2" s="4" t="n">
-        <v>45939.4575</v>
+        <v>45940.52256944445</v>
       </c>
     </row>
     <row r="3">
@@ -17149,7 +17157,7 @@
         <v/>
       </c>
       <c r="H2" s="7" t="n">
-        <v>26190000</v>
+        <v>26370000</v>
       </c>
       <c r="I2" s="7" t="n">
         <v>810000</v>
@@ -17160,7 +17168,7 @@
         </is>
       </c>
       <c r="K2" s="4" t="n">
-        <v>45939.4575</v>
+        <v>45940.52256944445</v>
       </c>
     </row>
     <row r="3">
@@ -17767,7 +17775,7 @@
         <v/>
       </c>
       <c r="H2" s="7" t="n">
-        <v>41730000</v>
+        <v>42460000</v>
       </c>
       <c r="I2" s="7" t="n">
         <v>930000</v>
@@ -17778,7 +17786,7 @@
         </is>
       </c>
       <c r="K2" s="4" t="n">
-        <v>45939.4575</v>
+        <v>45940.52256944445</v>
       </c>
     </row>
     <row r="3">
